--- a/surveys/svssurvey260914.xlsx
+++ b/surveys/svssurvey260914.xlsx
@@ -547,10 +547,10 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="27.25"/>
-    <col customWidth="1" min="2" max="2" width="52.88"/>
-    <col customWidth="1" min="3" max="3" width="19.38"/>
-    <col customWidth="1" min="4" max="4" width="37.63"/>
+    <col customWidth="1" min="1" max="1" width="7.25"/>
+    <col customWidth="1" min="2" max="2" width="41.38"/>
+    <col customWidth="1" min="3" max="3" width="74.75"/>
+    <col customWidth="1" min="4" max="4" width="55.63"/>
     <col customWidth="1" min="5" max="5" width="49.63"/>
     <col customWidth="1" min="6" max="11" width="18.88"/>
   </cols>
